--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 重构.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 重构.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="5"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
@@ -1854,15 +1854,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1871,6 +1862,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5690,30 +5690,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>458</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="25" t="s">
         <v>457</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="25" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>456</v>
       </c>
       <c r="B2" s="23" t="s">
@@ -5736,7 +5736,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="23" t="s">
         <v>305</v>
       </c>
@@ -5757,7 +5757,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="23" t="s">
         <v>447</v>
       </c>
@@ -5778,7 +5778,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="23" t="s">
         <v>443</v>
       </c>
@@ -5799,7 +5799,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="42" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>439</v>
       </c>
       <c r="B6" s="23" t="s">
@@ -5822,7 +5822,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="24" t="s">
         <v>435</v>
       </c>
       <c r="B7" s="23" t="s">
@@ -5845,7 +5845,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="27" t="s">
         <v>432</v>
       </c>
       <c r="B8" s="23" t="s">
@@ -5868,7 +5868,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="23" t="s">
         <v>317</v>
       </c>
@@ -5889,7 +5889,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>424</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -5912,7 +5912,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="23" t="s">
         <v>324</v>
       </c>
@@ -5933,7 +5933,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="28" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="23" t="s">
         <v>326</v>
       </c>
@@ -5954,7 +5954,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="23" t="s">
         <v>412</v>
       </c>
@@ -5975,7 +5975,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="23" t="s">
         <v>407</v>
       </c>
@@ -5996,7 +5996,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="23" t="s">
         <v>404</v>
       </c>
@@ -6017,7 +6017,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="23" t="s">
         <v>400</v>
       </c>
@@ -6038,7 +6038,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="23" t="s">
         <v>395</v>
       </c>
@@ -6092,288 +6092,288 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="26" t="s">
         <v>388</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="26" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="26" t="s">
         <v>387</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="26" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="26" t="s">
         <v>384</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="26" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="26" t="s">
         <v>383</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="26" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="26" t="s">
         <v>380</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="26" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="26" t="s">
         <v>379</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="26" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="26" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="26" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="26" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="26" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="26" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="26" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="26" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="26" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="26" t="s">
         <v>349</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="26" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="26" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="26" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="26" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="26" t="s">
         <v>326</v>
       </c>
     </row>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 重构.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 重构.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
